--- a/Phase - 12 Playwright Automation/DemoBlazePOM/data/login_data.xlsx
+++ b/Phase - 12 Playwright Automation/DemoBlazePOM/data/login_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EXPLEO SMARTCLIFF\Phase - 12 Playwright Automation\DemoBlazePOM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCED60D-0252-4532-9291-021F37A1E110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520ED4E4-7B45-4785-953E-3BB3B119B26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t>testName</t>
   </si>
@@ -60,21 +60,12 @@
     <t>Failure</t>
   </si>
   <si>
-    <t>Please fill out Username and Password</t>
-  </si>
-  <si>
     <t>Blank Password</t>
   </si>
   <si>
-    <t>'</t>
-  </si>
-  <si>
     <t>invalid password</t>
   </si>
   <si>
-    <t>Failue</t>
-  </si>
-  <si>
     <t>Wrong password.</t>
   </si>
   <si>
@@ -84,13 +75,16 @@
     <t>Invalid Email</t>
   </si>
   <si>
-    <t>Invaid mail</t>
-  </si>
-  <si>
     <t>User does not exist.</t>
   </si>
   <si>
     <t>Blank Fields</t>
+  </si>
+  <si>
+    <t>Invaidmail</t>
+  </si>
+  <si>
+    <t>Please fill out Username and Password.</t>
   </si>
 </sst>
 </file>
@@ -461,45 +455,43 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B5" s="2"/>
       <c r="C5" t="s">
         <v>6</v>
       </c>
@@ -507,41 +499,35 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="C6" s="2"/>
       <c r="D6" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
